--- a/Week5_DermaSmart_AI_Audit_Log.xlsx
+++ b/Week5_DermaSmart_AI_Audit_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LEARNING\Semester5\SWP391\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C3F0017-5D0C-4BD6-91EF-4A4F02040182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC30EBC4-3652-4EB2-865B-371C75FE606A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="208">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -651,19 +651,43 @@
     <t>Tôi có evidence?</t>
   </si>
   <si>
-    <t>001</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>003</t>
-  </si>
-  <si>
     <t>Nguyễn Quang Nhựt</t>
   </si>
   <si>
     <t>DE190056</t>
+  </si>
+  <si>
+    <t>Có – Thực hiện System Testing để kiểm tra toàn bộ chức năng.</t>
+  </si>
+  <si>
+    <t>✅ Có</t>
+  </si>
+  <si>
+    <t>✅ Test Cases</t>
+  </si>
+  <si>
+    <t>Có – Slide trình bày tập trung vào vấn đề, giải pháp và demo.</t>
+  </si>
+  <si>
+    <t>✅ Presentation</t>
+  </si>
+  <si>
+    <t>Có – Bổ sung Business Rules để hoàn thiện tài liệu SRS.</t>
+  </si>
+  <si>
+    <t>✅ SRS Document</t>
+  </si>
+  <si>
+    <t>Có – Chuẩn bị đầy đủ Frontend, Backend và Database cho demo.</t>
+  </si>
+  <si>
+    <t>✅ Deployment Guide</t>
+  </si>
+  <si>
+    <t>Có – Thiết kế Feedback gồm đánh giá sao và bình luận để dễ phân tích.</t>
+  </si>
+  <si>
+    <t>✅ ERD</t>
   </si>
 </sst>
 </file>
@@ -819,7 +843,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -854,12 +878,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -876,6 +894,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1082,15 +1103,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
     </row>
     <row r="3" spans="1:4" ht="14.85" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="18" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1099,7 +1120,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1107,7 +1128,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -1127,7 +1148,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="14.85" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="18" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1170,7 +1191,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="14.85" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="18" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1231,7 +1252,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="14.85" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="18" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1313,28 +1334,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
@@ -1696,24 +1717,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="16.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
@@ -1796,7 +1817,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.85" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="20"/>
+      <c r="A9" s="18"/>
       <c r="B9" s="13"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1840,7 +1861,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -1852,26 +1873,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="26" t="s">
         <v>157</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
     </row>
     <row r="4" spans="1:4" ht="14.85" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="B4" s="21"/>
+      <c r="B4" s="19"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
@@ -1950,7 +1971,7 @@
       <c r="D10" s="11"/>
     </row>
     <row r="12" spans="1:4" ht="14.85" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="18" t="s">
         <v>175</v>
       </c>
       <c r="B12" s="13"/>
@@ -2079,28 +2100,74 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
+      <c r="A28" s="27">
+        <v>33</v>
+      </c>
+      <c r="B28" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="D28" s="27" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
+      <c r="A29" s="27">
+        <v>34</v>
+      </c>
+      <c r="B29" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="C29" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="D29" s="27" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
+      <c r="A30" s="27">
+        <v>35</v>
+      </c>
+      <c r="B30" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="C30" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="D30" s="27" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="27">
+        <v>36</v>
+      </c>
+      <c r="B31" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="C31" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="D31" s="27" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="27">
+        <v>37</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="D32" s="27" t="s">
+        <v>207</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
